--- a/DigSite/New Arcaism/uarm 2026 a/maestría/Temas de investigación Maestría.xlsx
+++ b/DigSite/New Arcaism/uarm 2026 a/maestría/Temas de investigación Maestría.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitData\ArchaeologyJourney\DigSite\New Arcaism\uarm 2026 a\maestría\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA821D10-E6D5-4B28-8194-B7A791CFFC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781D517A-467D-424B-9662-487DDCFB8276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="210" windowWidth="14745" windowHeight="10920" xr2:uid="{855FE9F4-2AF7-44F3-A39D-004EC05E3142}"/>
+    <workbookView xWindow="3090" yWindow="120" windowWidth="17325" windowHeight="10920" xr2:uid="{855FE9F4-2AF7-44F3-A39D-004EC05E3142}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve"> N° </t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>aristoteles rawls, walzer, esferas justicia</t>
+  </si>
+  <si>
+    <t>mucho asunto procesal, poco aristóteles; libros 1 2 3 5 y 6? Mc Intyre?</t>
   </si>
 </sst>
 </file>
@@ -381,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +424,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -508,6 +517,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,6 +902,9 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
@@ -1077,7 +1092,7 @@
       <c r="B19" s="2">
         <v>18</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1099,7 +1114,7 @@
       <c r="B21" s="2">
         <v>20</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="1" t="s">
